--- a/data/trans_camb/IP07_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R2-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,45</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,99</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,43</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,75</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>2,21</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,03</t>
+          <t>-6,25; -0,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,0</t>
+          <t>-4,94; 1,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 5,53</t>
+          <t>-4,36; 3,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,28; -0,7</t>
+          <t>-0,86; 3,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 1,23</t>
+          <t>-2,47; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 2,57</t>
+          <t>-0,0; 6,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,34</t>
+          <t>-2,77; 0,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,76</t>
+          <t>-2,58; 0,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,0</t>
+          <t>-1,53; 3,16</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-52,86%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-36,16%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>106,46%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>471,01%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-52,86%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-39,43%</t>
+          <t>513,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; inf</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 210,69</t>
+          <t>-100,0; 397,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-71,83; 499,56</t>
+          <t>-76,61; 485,83</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,7</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,48</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,22</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,72</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,17</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 1,3</t>
+          <t>-5,14; 1,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,63</t>
+          <t>-4,69; 2,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 5,94</t>
+          <t>-3,42; 5,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 1,86</t>
+          <t>-4,88; 1,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,13</t>
+          <t>-5,78; 0,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 5,11</t>
+          <t>-3,29; 5,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,94</t>
+          <t>-3,71; 0,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,04</t>
+          <t>-4,0; 0,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 4,07</t>
+          <t>-1,88; 4,21</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-46,71%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-27,85%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,01%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-51,66%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-72,73%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>38,93%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-46,71%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-27,85%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-92,73; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,08; 150,64</t>
+          <t>-89,81; 144,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,85; 155,27</t>
+          <t>-92,18; 112,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,1; 468,27</t>
+          <t>-62,98; 416,97</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,69</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,84</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-0,92</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,36</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>-1,64</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,01</t>
+          <t>-7,49; -1,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 8,31</t>
+          <t>-5,8; 2,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,0</t>
+          <t>-4,6; 5,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,33; -1,29</t>
+          <t>-2,1; 3,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,85</t>
+          <t>-0,77; 8,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 4,21</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,2</t>
+          <t>-4,18; 0,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,36</t>
+          <t>-2,6; 3,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,89</t>
+          <t>-3,37; 1,89</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-50,38%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-24,87%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>61,67%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>270,56%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-50,38%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-28,96%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-68,86%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-44,54%</t>
+          <t>-45,19%</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 472,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 100,33</t>
+          <t>-100,0; 163,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 314,0</t>
+          <t>-78,57; 361,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 262,38</t>
+          <t>-100,0; 333,06</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,87</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,56</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,39</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,22</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>0,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,0</t>
+          <t>-0,92; 4,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 2,46</t>
+          <t>-1,95; 3,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 12,68</t>
+          <t>-2,2; 2,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,69</t>
+          <t>-1,03; 3,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,44</t>
+          <t>-1,68; 2,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,1</t>
+          <t>-1,55; 3,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,66</t>
+          <t>-0,44; 3,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,06</t>
+          <t>-1,2; 2,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 6,47</t>
+          <t>-1,15; 2,32</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>79,41%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23,87%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>82,14%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>12,81%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>153,09%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>79,41%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>23,87%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 522,35</t>
+          <t>-31,12; 407,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 394,13</t>
+          <t>-60,99; 282,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 1959,58</t>
+          <t>-66,33; 219,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 359,09</t>
+          <t>-54,56; 552,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,92; 334,84</t>
+          <t>-73,83; 515,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,03; 299,91</t>
+          <t>-77,54; 430,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 259,81</t>
+          <t>-15,17; 288,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 165,63</t>
+          <t>-45,93; 163,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 512,51</t>
+          <t>-43,44; 193,12</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-2,52</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,34</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-2,37</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,35</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,34</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-2,52</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,34</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-1,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 3,43</t>
+          <t>-6,49; 0,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 4,95</t>
+          <t>-6,57; 0,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 4,14</t>
+          <t>-6,4; 1,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 0,8</t>
+          <t>-3,12; 3,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 1,09</t>
+          <t>-2,26; 5,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 1,01</t>
+          <t>-3,15; 3,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,13</t>
+          <t>-3,93; 1,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,08</t>
+          <t>-3,28; 1,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,46</t>
+          <t>-3,58; 1,24</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-53,37%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-49,51%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-50,13%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>14,24%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>54,54%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-53,37%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-49,51%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-49,51%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-30,51%</t>
+          <t>-32,83%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,12; 54,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-65,93; 714,97</t>
+          <t>-87,98; 58,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-78,19; 725,85</t>
+          <t>-85,0; 73,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-85,85; 48,88</t>
+          <t>-73,22; 459,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-86,62; 85,04</t>
+          <t>-60,14; 716,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,49; 57,36</t>
+          <t>-79,87; 628,89</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-70,91; 54,86</t>
+          <t>-73,14; 56,69</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-64,86; 87,72</t>
+          <t>-62,58; 79,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-71,66; 63,96</t>
+          <t>-71,43; 63,44</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-2,79</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-4,42</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-2,24</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>4,78</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1,24</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>3,21</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-2,79</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-4,42</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,3</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,58</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,59; 12,54</t>
+          <t>-8,58; 1,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,26</t>
+          <t>-10,15; -0,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 8,51</t>
+          <t>-8,25; 3,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 1,65</t>
+          <t>0,77; 12,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,17; -0,73</t>
+          <t>-0,79; 5,24</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 2,94</t>
+          <t>0,15; 9,42</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 4,32</t>
+          <t>-2,74; 4,55</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 1,11</t>
+          <t>-4,58; 1,09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,82</t>
+          <t>-2,48; 4,23</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-51,71%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-81,94%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-41,5%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>609,54%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>157,86%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>409,43%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-51,71%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-81,94%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-42,7%</t>
+          <t>421,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 110,52</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 202,54</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 101,02</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 165,49</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-66,29; 260,93</t>
+          <t>-64,74; 287,58</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 131,1</t>
+          <t>-100,0; 122,16</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-68,32; 242,17</t>
+          <t>-65,43; 282,3</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,11</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,25</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-0,86</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,94</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,11</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,25</t>
+          <t>-2,49; 0,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,72</t>
+          <t>-2,81; 0,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,2; 4,71</t>
+          <t>-2,37; 0,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,21</t>
+          <t>-0,43; 2,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,17</t>
+          <t>-0,58; 1,81</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,59</t>
+          <t>-0,16; 2,57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,8</t>
+          <t>-1,05; 0,87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,55</t>
+          <t>-1,29; 0,57</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,91</t>
+          <t>-0,9; 1,17</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-33,3%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-37,41%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-25,64%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>62,43%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>32,8%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>112,36%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-33,3%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-37,41%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-25,43%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 230,93</t>
+          <t>-60,34; 9,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 166,26</t>
+          <t>-67,18; 5,23</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1,14; 411,4</t>
+          <t>-57,56; 23,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 9,5</t>
+          <t>-19,29; 218,94</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-63,49; 8,03</t>
+          <t>-31,81; 185,91</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 25,91</t>
+          <t>-13,32; 242,27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 40,95</t>
+          <t>-35,06; 46,7</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-46,42; 29,1</t>
+          <t>-43,97; 28,45</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 88,38</t>
+          <t>-31,67; 60,61</t>
         </is>
       </c>
     </row>
